--- a/output/pdf_financials_xlsx/VROY.xlsx
+++ b/output/pdf_financials_xlsx/VROY.xlsx
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.155278</v>
       </c>
     </row>
     <row r="93">
@@ -3170,7 +3170,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VROY.xlsx
+++ b/output/pdf_financials_xlsx/VROY.xlsx
@@ -543,7 +543,7 @@
         <v>0.000468</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.375889</v>
+        <v>0.554639</v>
       </c>
     </row>
     <row r="8">
@@ -4273,7 +4273,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -5827,7 +5831,11 @@
           <t>Directors’ fees 10</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
